--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260813.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>137,885</t>
+          <t>136,485</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.88%</t>
+          <t>28.76%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>529,993,964</t>
+          <t>524,888,768</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.28%</t>
+          <t>8.22%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,685</t>
+          <t>15,485</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.21%</t>
+          <t>8.19%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>99,870</t>
+          <t>98,870</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.70%</t>
+          <t>7.78%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>50,715</t>
+          <t>50,215</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.62%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>121,295</t>
+          <t>119,995</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.20%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>59,680</t>
+          <t>58,980</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.78%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,615</t>
+          <t>64,815</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,273</t>
+          <t>18,073</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>45,265</t>
+          <t>44,665</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,725</t>
+          <t>19,525</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>77,045</t>
+          <t>76,245</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>20,295</t>
+          <t>20,095</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>31,560</t>
+          <t>31,260</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>51,075</t>
+          <t>50,575</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -968,73 +968,73 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,558</t>
+          <t>35,880</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,280</t>
+          <t>19,230</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>19,430</t>
+          <t>26,258</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>59,448</t>
+          <t>58,848</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,44 +1063,44 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,536</t>
+          <t>7,890</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,990</t>
+          <t>9,436</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>21,308</t>
+          <t>21,108</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>127,055</t>
+          <t>125,755</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>19,617</t>
+          <t>19,517</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,455</t>
+          <t>18,255</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,44 +1195,44 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,871</t>
+          <t>1,767,405</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>37,590</t>
+          <t>15,671</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>43,350</t>
+          <t>42,850</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,22 +1261,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,482,418</t>
+          <t>37,190</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,765</t>
+          <t>11,665</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>32,874,620</t>
+          <t>83,690,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>604,987</t>
+          <t>2,018,032</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
